--- a/data_raw/re_A0302_房地产开发投资额_亿元.xlsx
+++ b/data_raw/re_A0302_房地产开发投资额_亿元.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>房地产开发投资额(亿元)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2254 +420,2426 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>房地产开发投资额(亿元)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1275.5938</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1307.5256</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1435.7349</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1462.0724</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1980.68</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>2253.8314</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>2381.3574</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>2819.5915</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>3206.4773</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>3468.9415</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>3709.0311</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>3856.5278</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>4033.1832</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>4231.3761</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>4698.7486</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>5035.1841</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>4979.5393</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>6062.0387</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>6228.9059</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>53.1084</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>81.7958</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>99.9631</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>113.2955</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>143.03</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>194.292</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>220.6935</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>270.5936</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>329.976</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>366.867</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>362.4975</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>422.7395</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>659.1507</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>544.1344</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>550.4005</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>537.7692</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>311.9536</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>358.0816</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>366.6525</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>53.8417</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>74.44759999999999</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>92.4272</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>99.0776</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>118.28</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>154.8444</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>209.7401</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>257.435</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>317.0837</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>320.5558</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>391.15</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>418.2571</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>575.218</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>550.6744</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>553.7696999999999</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>602.763</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>486.4549</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>401.5446</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>297.3123</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1719.865</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1995.8206</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1908.7387</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2337.7124</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>2901.07</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>3036.3118</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>3153.4419</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>3483.4045</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>3715.3341</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>4177.0481</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>4000.5729</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>3692.5416</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>3873.3513</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>3838.3805</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>3938.7093</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>4139.0288</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>4178.4569</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>4202.4126</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>3758.2939</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>351.1742</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>445.973</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>508.1669</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>595.6796000000001</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>748.35</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>871.7601</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>971.9642</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>1037.7148</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>1125.49</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>1429.0194</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>1845.6004</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>2170.2088</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>2354.1664</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>2501.2573</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>2631.3994</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>2719.8034</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>2758.7699</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>2764.3625</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>2190.6311</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>139.0742</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>187.463</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>202.4577</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>226.725</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>322.82</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>392.4234</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>362.7301</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>416.3709</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>551.8214</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>657.1897</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>853.9976</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>958.0867</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>1106.3588</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>1461.0763</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>1378.2011</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>1359.9484</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>743.8271999999999</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>496.4122</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>444.1185</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>110.7512</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>125.602</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>163.304</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>198.2468</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>230.15</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>279.8933</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>344.3607</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>406.1358</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>414.0682</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>485.3714</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>674.598</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>790.6914</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>890.4296000000001</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>913.0359</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>971.5664</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>975.8427</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>787.4183</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>496.6266</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>473.4938</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>213.9308</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>345.7362</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>327.016</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>267.4171</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>396.13</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>438.1217</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>518.8791</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>531.8029</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>704.0636</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>774.0727000000001</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>765.797</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>879.8628</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>884.5759</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>899.5349</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>1055.7575</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>1069.6582</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>1064.783</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>1435.5972</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>976.0621</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>281.8051</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>387.5325</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>567.1624</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>670.3559</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>819.03</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>889.6017000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>913.8031</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>1105.8109</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>1127.3511</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>1259.1353</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>1352.5944</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>1557.4051</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>1527.174</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>1556.0807</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1546.992</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>1466.4185</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>1457.0872</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>1544.6256</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>1582.4578</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>94.99339999999999</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>129.8346</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>177.0684</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>178.9909</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>254.35</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>330.0329</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>447.9861</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>581.6832000000001</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>563.1305</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>509.0452</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>520.52</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>238.3997</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>174.25</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>175.2248</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>246.8943</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>270.7185</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>219.0885</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>234.5798</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>280.9184</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>157.8323</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>187.4184</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>215.7614</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>279.2251</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>360.74</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>570.4558</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>789.0366</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>857.9379</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>686.6631</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>593.9814</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>512.1301</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>498.5896</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>584.989</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>620.449</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>622.0494</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>531.3706</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>341.0461</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>228.2074</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>179.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>337.2348</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>407.8312</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>495.816</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>578.9421</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>768.02</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>1107.463</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>1396.5204</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>1710.3585</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>1429.3353</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>897.4595</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>535.1742</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>566.6385</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>688.5137999999999</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>711.056</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>753.0643</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>728.9512</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>608.8381000000001</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>458.1274</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>362.4196</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>402.3184</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>505.2956</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>653.7248</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>735.1836</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>866.64</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1080.2492</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>1259.9969</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>1480.8152</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>1699.6496</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>1871.5464</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>2300.0107</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>2233.3936</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>2424.4892</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>2727.8199</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>2608.5378</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>2769.9822</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>2127.9393</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>1232.0409</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>1262.2318</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>80.3198</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>94.8249</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>121.173</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>165.0122</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>241.09</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>310.5476</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>359.2367</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>416.2332</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>469.6758</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>597.8342</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>681.9017</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>470.6283</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>529.4127999999999</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>696.5445999999999</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>714.8194</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>665.4742</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>541.4112</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>518.2329</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>507.6819</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>313.581</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>332.8941</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>307.7538</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>374.5119</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>557.27</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>711.4644</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>884.3514</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>1123.1401</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>1328.139</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>1228.8427</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1270.3341</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>1374.4702</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>1587.4687</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>1703.5861</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1818.8785</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>2075.5857</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>2131.6845</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>2218.6125</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>1873.2012</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>556.7893</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>703.8031</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>763.5376</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>817.3449000000001</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>983.66</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1305.5605</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1370.4511</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1572.4289</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1816.1529</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>2137.5891</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>2540.8549</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>2702.8935</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>2701.9323</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>3102.2573</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>3293.9465</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>3626.4398</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>3431.8992</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>3311.4473</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>3066.032</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>613.6351</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>905.28</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>923.5118</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>945.1356</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>1278.34</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>1588.2175</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>1889.2305</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>2111.2499</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>2215.5331</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>2435.2535</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>2638.8901</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>2492.651</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>2273.1625</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>2611.712</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>2847.6439</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>3142.3847</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>3271.7154</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>2449.5883</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>2415.3797</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L19">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
         <v>44.5423</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>188.9329</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>228.0217</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>274.2017</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>382.1456</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>437.14</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>633.0343</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>919.0732</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>1291.706</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>1492.6246</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>1451.3067</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>1530.4999</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>1683.3325</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>1839.7925</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>2096.251</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>2263.708</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>2149.0561</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>1486.9979</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>634.2582</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>492.7403</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>442.6534</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>518.7904</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>615.4059999999999</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>704.6752</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>956.2</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>1201.5116</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>1597.3611</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>1853.2841</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>2301.9788</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>2472.5985</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>2606.409</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>2734.2031</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>3068.8988</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>3396.746</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>3575.3272</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>3628.3268</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>3889.0957</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>4400.6881</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>4222.1709</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>366.1516</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>459.7498</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>560.3605</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>778.5946</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1017.4</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1282.2494</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1574.8605</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1905.6</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>2353.6263</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>2581.7857</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>2517.435</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>2686.3358</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>2780.0098</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>2966.206</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>2777.1514</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>3254.6233</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>3366.7892</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>3446.8756</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>3332.08</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>538.2914</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>730.3637</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1010.9145</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1188.7007</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1450.08</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1684.7242</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>1942.9642</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>2184.0129</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>1975.8182</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>1337.6632</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>709.6706</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>814.2371000000001</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>996.721</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>1174.804</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>1235.8866</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>1222.6107</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>940.3111</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>610.8616</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>510.4719</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>160.0507</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>193.2069</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>274.1166</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>332.5576</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>484.5</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>528.9193</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>664.0112</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>721.7682</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>917.5398</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>1014.3957</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>1163.9381</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>1232.6305</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>1370.4256</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>1489.3781</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>1707.6304</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>1928.0018</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>1830.8037</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>1489.2441</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>1557.5545</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>50.473</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>59.9709</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>76.1741</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>78.4406</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>103.79</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>144.6436</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>175.6639</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>256.4025</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>300.4725</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>456.3949</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>551.0947</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>603.2485</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>609.417</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>480.7292</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>443.6699</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>452.4505</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>438.0858</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>482.2485</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>442.6999</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>462.094</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>461.0422</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>440.4897</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>437.459</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>458.47</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>514.7362000000001</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>736.8421</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>876.9002</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>1069.4855</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>1331.0333</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>1756.5209</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>2130.862</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>2640.7142</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>3041.6518</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>3537.8449</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>2979.0776</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>3391.5439</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>3787.462</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>3219.4479</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>132.1452</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>197.537</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>280.3979</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>378.2171</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>538</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>789.1413</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>833.2125</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>928.1491</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>1025.3286</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>965.1327</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>1015.765</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>1212.272</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>1010.7146</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>887.6439</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>926.4906999999999</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>951.3162</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>767.2042</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>521.0054</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>516.1055</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>296.7821</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>376.4663</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>313.6079</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>361.7991</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>670.6900000000001</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>963.4087</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>972.2667</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>1264.7907</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>1455.0729</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>1381.1248</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>1679.4355</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>1694.1798</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>1439.6795</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>1812.7732</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>2070.2316</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>2248.8134</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>1663.8713</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>1085.9746</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>944.5512</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>29.381</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>31.5991</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>45.3923</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>63.8393</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>118.5454</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>160.1412</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>195.5784</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>246.8649</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>280.4295</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>316.4971</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>351.3337</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>292.2514</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>290.9923</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>270.4004</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>265.7844</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>169.9264</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>113.1744</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>91.9545</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>285.7605</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>387.3342</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>545.7103</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>694.2341</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>842.34</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>996.1201</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>1269.9344</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>1572.6491</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>1742.28</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>1820.8541</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>1955.8202</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>2234.8421</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>2213.684</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>2008.2971</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>2064.6273</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>1975.281</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>2061.8497</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>2052.0303</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>2144.7639</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>107.6936</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>135.4416</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>170.1116</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>210.3225</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>310.47</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>460.4941</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>901.0264</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>978.0165</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>1010.375</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>1001.0275</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>927.3162</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>1024.0915</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>985.2557</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>1175.374</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>1291.366</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>1120.0454</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>753.0242</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>417.7774</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>437.4799</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>229.8933</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>298.7582</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>434.9566</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>512.3150000000001</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>775.16</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>926.3083</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>1095.1368</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>1445.3279</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>1743.5127</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>2000.1954</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>2778.9452</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>3358.8413</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>3258.409</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>3349.8577</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>3428.7764</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>3088.8788</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>2158.5894</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>1863.8735</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>1864.3321</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>629.669</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>849.8966</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>990.997</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>1238.9125</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>1620.26</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>2015.1</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>2508.35</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>3012.7838</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>3630.2331</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>3751.2812</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>3725.9452</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>3980.0837</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>4248.7612</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>4439.3034</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>4351.9565</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>4354.9551</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>3216.8663</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>2796.7094</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>2565.7881</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>57.6808</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>62.7154</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>78.6159</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>99.9584</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>172.13</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>214.7834</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>275.7023</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>330.8094</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>388.8952</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>409.1711</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>474.9414</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>402.8246</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>295.2457</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>275.3536</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>311.4257</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>325.7863</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>273.7973</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>266.4209</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>253.2425</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>171.8428</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>259.4979</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>352.8921</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>443.9252</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>542.76</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>666.4177</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>649.6535</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>611.7822</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>532.5676999999999</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>501.3222</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>596.6477</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>573.7761</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>778.6345</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>876.788</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>996.0687</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>1052.3427</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>661.9589999999999</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>551.1617</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>412.5126</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>303.8612</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>407.0472</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>493.2729</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>497.3492</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>684.1</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>926.0095</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>1034.3503</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>1157.6292</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>1313.6182</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>1006.8414</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>1260.5475</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>1493.4441</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>1508.719</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>1672.9645</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>1869.8777</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>2236.8754</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>2281.4846</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>1888.7011</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>1712.9792</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>268.3631</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>322.3547</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>380.5652</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>459.4829</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>602.4400000000001</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>785.8221</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>932.0986</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>1048.5229</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>1117.7297</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>1122.3458</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1369.1425</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>1330.5432</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>1485.2089</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>1803.8081</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>2045.1153</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>1982.3415</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>1789.8736</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>1729.3153</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>1511.785</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>